--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25595.22</v>
+        <v>24779.07</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>64861.44</v>
+        <v>62793.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29450.27</v>
+        <v>28511.19</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>38100.59</v>
+        <v>37349.19</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>21620.48</v>
+        <v>21051.14</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>126768.29</v>
+        <v>123430.06</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77667.38</v>
+        <v>75622.14</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>61900.28</v>
+        <v>60270.24</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13684.26</v>
+        <v>13436.1</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>30285.23</v>
+        <v>29736.01</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>21557.37</v>
+        <v>21620.12</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>42225.17</v>
+        <v>42400.66</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>26973.2</v>
+        <v>27305.16</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>41783.23</v>
+        <v>42297.47</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>21857.2</v>
+        <v>22148.18</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>41573.79</v>
+        <v>42116.32</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>39677.35</v>
+        <v>40195.13</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>42659.19</v>
+        <v>43144.32</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30285.23</v>
+        <v>30629.64</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13834.64</v>
+        <v>13959.27</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>79354.7</v>
+        <v>79604.38</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>14420.84</v>
+        <v>14480.61</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36254.69</v>
+        <v>36404.96</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>36720.14</v>
+        <v>36796.21</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>39677.35</v>
+        <v>39506.9</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>13486.6</v>
+        <v>13428.66</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>39350.52</v>
+        <v>39181.48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC abr-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -869,7 +869,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DEPTO. BIENESTAR SOCIAL DE LA ARMADA (I)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +948,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1013,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1139,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1204,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1237,7 +1269,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1298,7 +1334,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1359,7 +1399,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1464,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1590,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1655,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1720,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1846,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2033,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2098,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2163,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2228,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/abr-2026.xlsx
@@ -1972,7 +1972,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
